--- a/stories/arbres/TREE-REL-010.xlsx
+++ b/stories/arbres/TREE-REL-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, un téléphone s'allume. Quelqu'un veut une photo. Lila regarde papa. Maman arrivera à la gare. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Un téléphone rouge s'allume. On parle d'une photo. C'est le rouge. Un galet est lisse dans la main. Lila s'approche, sans courir. Maman n'est pas loin. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Il y a un téléphone. Que fait-on avant une photo ? Avec rouge.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon rouge, après rouge. Le vent fait bouger un rideau. Lila range un peu autour du ballon rouge. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2583,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le rouge et le ballon rouge. La tasse est encore tiède. On dit merci. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila salue le chat un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le rouge et le ballon rouge. Le parquet craque un tout petit peu. On écoute jusqu'au bout. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila salue le chien un instant. Puis elle reprend, calme. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le rouge et le ballon rouge. Une abeille bourdonne loin. On attend un petit moment. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila salue la poule un instant. Puis elle reprend, calme. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3752,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau bleu, après rouge. La tasse est encore tiède. Lila range un peu autour du seau bleu. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3943,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4110,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le rouge et le seau bleu. Un gravier roule sous une semelle. On pose les fesses sur une chaise. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4277,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4444,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le rouge et le seau bleu. La fenêtre tremble un tout petit peu. On sourit un peu. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4611,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4778,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le rouge et le seau bleu. Ça sent le savon de maman. On boit une gorgée d'eau. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4945,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5112,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou, après rouge. Le coussin est moelleux. Lila montre le doudou à papa. Elle nomme ce qu'elle sent. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5303,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5470,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le rouge et le doudou. Un pigeon roucoule. On essuie une miette. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5637,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5804,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le rouge et le doudou. La cuillère tinte. On referme un livre. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5971,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6138,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le rouge et le doudou. Le ballon est un peu poudreux. On pose un jouet à sa place. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6305,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6472,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Un téléphone bleu vibre. On parle d'une photo. Lila s'occupe de bleu. Le vent glisse sur les joues. Papa sourit. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6653,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Il y a un téléphone. Que fait-on avant une photo ? Avec bleu.</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6826,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila répète le mot. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7017,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6997,6 +7184,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon rouge, après bleu. Le soleil chauffe un peu le nez. Le ballon rouge reste à sa place. Lila aussi. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7375,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7345,6 +7542,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le bleu et le ballon rouge. Une goutte de pluie sèche déjà. On marche tout doucement. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila dit merci à papa. Maman sourit. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7709,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7876,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le bleu et le ballon rouge. Le banc est tiède. On se tait une seconde. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila dit merci à papa. Maman sourit. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8043,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8210,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le bleu et le ballon rouge. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila dit merci à papa. Maman sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8377,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8544,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau bleu, après bleu. Ça sent le pain encore chaud. Lila range un peu autour du seau bleu. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8735,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8902,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le bleu et le seau bleu. Une feuille tourne et tombe. On s'assoit près de l'adulte. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chat à sa place. Lila est près de papa. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9069,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9236,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le bleu et le seau bleu. L'eau fait un tout petit bruit. On nomme ce qu'on sent. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chien à sa place. Lila est près de papa. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9403,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9570,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le bleu et le seau bleu. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse la poule à sa place. Lila est près de papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9737,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9904,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou, après bleu. La page du livre est lisse. Le doudou est là. Lila pose les mains à vue, loin de l'autre. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10095,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9985,6 +10262,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le bleu et le doudou. Une plume vole. On range les chaussures. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chat à sa place. Lila est près de papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10429,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10596,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le bleu et le doudou. Le pain croustille. On met le doudou près de soi. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chien à sa place. Lila est près de papa. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10763,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10930,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le bleu et le doudou. La laine du doudou est douce. On écoute le cœur, tout doux. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse la poule à sa place. Lila est près de papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11097,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11264,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Un téléphone vert reste dans une poche. On parle d'une photo. Voilà vert. Un pigeon roucoule. Lila pose les pieds par terre, près de papa. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11445,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Il y a un téléphone. Que fait-on avant une photo ? Avec vert.</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11618,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11809,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11511,7 +11838,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le ballon rouge, après vert. La clochette de la porte tinte. Lila touche le ballon rouge tout doucement. Papa dit : je suis là. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+          <t>Lila a choisi le ballon rouge, après vert. La clochette de la porte tinte. Lila touche le ballon rouge tout doucement. Je suis là. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11649,6 +11976,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon rouge, après vert. La clochette de la porte tinte. Lila touche le ballon rouge tout doucement.
+papa|Je suis là. On doit demander avant une photo.
+narrateur|Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12169,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12336,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le vert et le ballon rouge. Un galet est lisse dans la main. On secoue les mains, loin. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12503,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12670,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le vert et le ballon rouge. Le train souffle au loin. On pose le sac. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12837,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13004,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le vert et le ballon rouge. Une vache meugle, loin. On dit le mot de l'émotion. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13171,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13338,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau bleu, après vert. La page du livre est lisse. Lila range un peu autour du seau bleu. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13529,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13317,6 +13696,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le vert et le seau bleu. Un grillon chante, tout petit. On invite d'une petite voix. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13863,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14030,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le vert et le seau bleu. Le bois de la table est lisse. On attend la réponse. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14197,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14364,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le vert et le seau bleu. Une goutte tombe dans l'évier. On propose une autre idée. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14531,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14151,7 +14560,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le doudou, après vert. Le vent fait bouger un rideau. Lila touche le doudou tout doucement. Papa dit : je suis là. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+          <t>Lila a choisi le doudou, après vert. Le vent fait bouger un rideau. Lila touche le doudou tout doucement. Je suis là. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14289,6 +14698,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou, après vert. Le vent fait bouger un rideau. Lila touche le doudou tout doucement.
+papa|Je suis là. On doit demander avant une photo.
+narrateur|Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14891,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15058,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le vert et le doudou. Le toboggan est un peu froid. On va vers papa ou maman. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15225,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15392,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le vert et le doudou. La clochette de la porte tinte. On dit stop, tout clair. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15559,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15726,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le vert et le doudou. Ça sent le thym du jardin. On s'éloigne d'un pas. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15893,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15933,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-010.xlsx
+++ b/stories/arbres/TREE-REL-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Dans le train, un téléphone s'allume. Quelqu'un veut une photo. Lila regarde papa. Maman arrivera à la gare. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Un téléphone rouge s'allume. On parle d'une photo. C'est le rouge. Un galet est lisse dans la main. Lila s'approche, sans courir. Maman n'est pas loin. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Il y a un téléphone. Que fait-on avant une photo ? Avec rouge.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Oui. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Lila a choisi le ballon rouge, après rouge. Le vent fait bouger un rideau. Lila range un peu autour du ballon rouge. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2755,6 +2772,7 @@
           <t>narrateur|Lila rejoint le chat, après le rouge et le ballon rouge. La tasse est encore tiède. On dit merci. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila salue le chat un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3108,11 @@
           <t>narrateur|Lila rejoint le chien, après le rouge et le ballon rouge. Le parquet craque un tout petit peu. On écoute jusqu'au bout. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila salue le chien un instant. Puis elle reprend, calme. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3448,7 @@
           <t>narrateur|Lila rejoint la poule, après le rouge et le ballon rouge. Une abeille bourdonne loin. On attend un petit moment. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila salue la poule un instant. Puis elle reprend, calme. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3784,7 @@
           <t>narrateur|Lila a choisi le seau bleu, après rouge. La tasse est encore tiède. Lila range un peu autour du seau bleu. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3974,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4115,6 +4148,7 @@
           <t>narrateur|Lila rejoint le chat, après le rouge et le seau bleu. Un gravier roule sous une semelle. On pose les fesses sur une chaise. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4282,6 +4316,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4449,6 +4484,11 @@
           <t>narrateur|Lila rejoint le chien, après le rouge et le seau bleu. La fenêtre tremble un tout petit peu. On sourit un peu. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4616,6 +4656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4783,6 +4824,7 @@
           <t>narrateur|Lila rejoint la poule, après le rouge et le seau bleu. Ça sent le savon de maman. On boit une gorgée d'eau. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4950,6 +4992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5117,6 +5160,7 @@
           <t>narrateur|Lila a choisi le doudou, après rouge. Le coussin est moelleux. Lila montre le doudou à papa. Elle nomme ce qu'elle sent. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5350,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5475,6 +5524,7 @@
           <t>narrateur|Lila rejoint le chat, après le rouge et le doudou. Un pigeon roucoule. On essuie une miette. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5642,6 +5692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5809,6 +5860,11 @@
           <t>narrateur|Lila rejoint le chien, après le rouge et le doudou. La cuillère tinte. On referme un livre. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5976,6 +6032,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6143,6 +6200,7 @@
           <t>narrateur|Lila rejoint la poule, après le rouge et le doudou. Le ballon est un peu poudreux. On pose un jouet à sa place. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On écoute le silence une seconde. Lila est assise. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6310,6 +6368,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6477,6 +6536,7 @@
           <t>narrateur|Un téléphone bleu vibre. On parle d'une photo. Lila s'occupe de bleu. Le vent glisse sur les joues. Papa sourit. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6660,6 +6720,7 @@
           <t>narrateur|Il y a un téléphone. Que fait-on avant une photo ? Avec bleu.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6831,6 +6892,7 @@
           <t>narrateur|Oui. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7022,6 +7084,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7189,6 +7252,7 @@
           <t>narrateur|Lila a choisi le ballon rouge, après bleu. Le soleil chauffe un peu le nez. Le ballon rouge reste à sa place. Lila aussi. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7442,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7547,6 +7616,7 @@
           <t>narrateur|Lila rejoint le chat, après le bleu et le ballon rouge. Une goutte de pluie sèche déjà. On marche tout doucement. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila dit merci à papa. Maman sourit. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7714,6 +7784,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7881,6 +7952,11 @@
           <t>narrateur|Lila rejoint le chien, après le bleu et le ballon rouge. Le banc est tiède. On se tait une seconde. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila dit merci à papa. Maman sourit. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8048,6 +8124,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8215,6 +8292,7 @@
           <t>narrateur|Lila rejoint la poule, après le bleu et le ballon rouge. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila dit merci à papa. Maman sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8382,6 +8460,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8549,6 +8628,7 @@
           <t>narrateur|Lila a choisi le seau bleu, après bleu. Ça sent le pain encore chaud. Lila range un peu autour du seau bleu. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8818,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8907,6 +8992,7 @@
           <t>narrateur|Lila rejoint le chat, après le bleu et le seau bleu. Une feuille tourne et tombe. On s'assoit près de l'adulte. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chat à sa place. Lila est près de papa. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9074,6 +9160,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9241,6 +9328,11 @@
           <t>narrateur|Lila rejoint le chien, après le bleu et le seau bleu. L'eau fait un tout petit bruit. On nomme ce qu'on sent. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chien à sa place. Lila est près de papa. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9408,6 +9500,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9575,6 +9668,7 @@
           <t>narrateur|Lila rejoint la poule, après le bleu et le seau bleu. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse la poule à sa place. Lila est près de papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9742,6 +9836,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9909,6 +10004,7 @@
           <t>narrateur|Lila a choisi le doudou, après bleu. La page du livre est lisse. Le doudou est là. Lila pose les mains à vue, loin de l'autre. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10194,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10267,6 +10368,7 @@
           <t>narrateur|Lila rejoint le chat, après le bleu et le doudou. Une plume vole. On range les chaussures. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chat à sa place. Lila est près de papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10434,6 +10536,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10601,6 +10704,11 @@
           <t>narrateur|Lila rejoint le chien, après le bleu et le doudou. Le pain croustille. On met le doudou près de soi. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse le chien à sa place. Lila est près de papa. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10768,6 +10876,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10935,6 +11044,7 @@
           <t>narrateur|Lila rejoint la poule, après le bleu et le doudou. La laine du doudou est douce. On écoute le cœur, tout doux. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. On laisse la poule à sa place. Lila est près de papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11102,6 +11212,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11269,6 +11380,7 @@
           <t>narrateur|Un téléphone vert reste dans une poche. On parle d'une photo. Voilà vert. Un pigeon roucoule. Lila pose les pieds par terre, près de papa. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11452,6 +11564,7 @@
           <t>narrateur|Il y a un téléphone. Que fait-on avant une photo ? Avec vert.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11623,6 +11736,7 @@
           <t>narrateur|Oui. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11814,6 +11928,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11983,6 +12098,7 @@
 narrateur|Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12172,6 +12288,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12341,6 +12462,7 @@
           <t>narrateur|Lila rejoint le chat, après le vert et le ballon rouge. Un galet est lisse dans la main. On secoue les mains, loin. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12508,6 +12630,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12675,6 +12798,11 @@
           <t>narrateur|Lila rejoint le chien, après le vert et le ballon rouge. Le train souffle au loin. On pose le sac. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12842,6 +12970,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13009,6 +13138,7 @@
           <t>narrateur|Lila rejoint la poule, après le vert et le ballon rouge. Une vache meugle, loin. On dit le mot de l'émotion. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13176,6 +13306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13343,6 +13474,7 @@
           <t>narrateur|Lila a choisi le seau bleu, après vert. La page du livre est lisse. Lila range un peu autour du seau bleu. Elle respire. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13532,6 +13664,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13701,6 +13838,7 @@
           <t>narrateur|Lila rejoint le chat, après le vert et le seau bleu. Un grillon chante, tout petit. On invite d'une petite voix. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13868,6 +14006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14035,6 +14174,11 @@
           <t>narrateur|Lila rejoint le chien, après le vert et le seau bleu. Le bois de la table est lisse. On attend la réponse. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14202,6 +14346,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14369,6 +14514,7 @@
           <t>narrateur|Lila rejoint la poule, après le vert et le seau bleu. Une goutte tombe dans l'évier. On propose une autre idée. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14536,6 +14682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14705,6 +14852,7 @@
 narrateur|Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14894,6 +15042,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15063,6 +15216,7 @@
           <t>narrateur|Lila rejoint le chat, après le vert et le doudou. Le toboggan est un peu froid. On va vers papa ou maman. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15230,6 +15384,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15397,6 +15552,11 @@
           <t>narrateur|Lila rejoint le chien, après le vert et le doudou. La clochette de la porte tinte. On dit stop, tout clair. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15564,6 +15724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15731,6 +15892,7 @@
           <t>narrateur|Lila rejoint la poule, après le vert et le doudou. Ça sent le thym du jardin. On s'éloigne d'un pas. On doit demander avant une photo. Un adulte gardu téléphone. Ce n'est pas pour rire de l'autre. Lila demande à papa. Lila serre la main de papa, tout doux. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15898,6 +16060,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15916,7 +16079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15940,6 +16103,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15954,7 +16131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16141,6 +16318,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
